--- a/Project 1 Data Quality Assessment/D3 Physical rationality and rate constraints/outputs/validation/D3_temperature_conditioned_DO_upper.xlsx
+++ b/Project 1 Data Quality Assessment/D3 Physical rationality and rate constraints/outputs/validation/D3_temperature_conditioned_DO_upper.xlsx
@@ -13,14 +13,16 @@
     <sheet name="phase_validation" sheetId="4" r:id="rId4"/>
     <sheet name="cross_line_transfer" sheetId="5" r:id="rId5"/>
     <sheet name="alpha_sensitivity" sheetId="6" r:id="rId6"/>
-    <sheet name="exclusions" sheetId="7" r:id="rId7"/>
+    <sheet name="alpha_CI_scenarios" sheetId="7" r:id="rId7"/>
+    <sheet name="envelope_comparison" sheetId="8" r:id="rId8"/>
+    <sheet name="exclusions" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1381" uniqueCount="131">
   <si>
     <t>temperature_source</t>
   </si>
@@ -359,6 +361,42 @@
   </si>
   <si>
     <t>alpha_multiplier</t>
+  </si>
+  <si>
+    <t>alpha_scenario</t>
+  </si>
+  <si>
+    <t>alpha_value</t>
+  </si>
+  <si>
+    <t>sensitivity_role</t>
+  </si>
+  <si>
+    <t>bootstrap_lower</t>
+  </si>
+  <si>
+    <t>point_estimate</t>
+  </si>
+  <si>
+    <t>bootstrap_upper</t>
+  </si>
+  <si>
+    <t>bootstrap_interval_propagation_not_production_parameter_selection</t>
+  </si>
+  <si>
+    <t>envelope_model</t>
+  </si>
+  <si>
+    <t>comparison_role</t>
+  </si>
+  <si>
+    <t>temperature_conditioned</t>
+  </si>
+  <si>
+    <t>fixed_8_mg_L</t>
+  </si>
+  <si>
+    <t>prespecified_method_comparison_not_threshold_selection</t>
   </si>
   <si>
     <t>exclusion</t>
@@ -8941,6 +8979,6195 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z55"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:26">
+      <c r="A1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26">
+      <c r="A2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D2">
+        <v>0.218586137707535</v>
+      </c>
+      <c r="E2">
+        <v>260820</v>
+      </c>
+      <c r="F2">
+        <v>49373</v>
+      </c>
+      <c r="G2">
+        <v>4387</v>
+      </c>
+      <c r="H2">
+        <v>572</v>
+      </c>
+      <c r="I2">
+        <v>0.01682002913886972</v>
+      </c>
+      <c r="J2">
+        <v>0.01158527940372268</v>
+      </c>
+      <c r="M2">
+        <v>532</v>
+      </c>
+      <c r="N2">
+        <v>25</v>
+      </c>
+      <c r="O2">
+        <v>0.04699248120300752</v>
+      </c>
+      <c r="R2" t="b">
+        <v>1</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="s">
+        <v>99</v>
+      </c>
+      <c r="V2">
+        <v>2.007795667568483</v>
+      </c>
+      <c r="W2">
+        <v>1.704102644839638</v>
+      </c>
+      <c r="X2">
+        <v>2.289856370596061</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26">
+      <c r="A3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D3">
+        <v>0.218586137707535</v>
+      </c>
+      <c r="E3">
+        <v>18318</v>
+      </c>
+      <c r="F3">
+        <v>6240</v>
+      </c>
+      <c r="G3">
+        <v>195</v>
+      </c>
+      <c r="H3">
+        <v>34</v>
+      </c>
+      <c r="I3">
+        <v>0.01064526695054045</v>
+      </c>
+      <c r="J3">
+        <v>0.005448717948717948</v>
+      </c>
+      <c r="M3">
+        <v>61</v>
+      </c>
+      <c r="N3">
+        <v>4</v>
+      </c>
+      <c r="O3">
+        <v>0.06557377049180328</v>
+      </c>
+      <c r="R3" t="b">
+        <v>1</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="s">
+        <v>100</v>
+      </c>
+      <c r="V3">
+        <v>2.127691163298016</v>
+      </c>
+      <c r="W3">
+        <v>2.094680295556264</v>
+      </c>
+      <c r="X3">
+        <v>2.161193246873688</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26">
+      <c r="A4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4">
+        <v>0.218586137707535</v>
+      </c>
+      <c r="E4">
+        <v>84960</v>
+      </c>
+      <c r="F4">
+        <v>39720</v>
+      </c>
+      <c r="G4">
+        <v>906</v>
+      </c>
+      <c r="H4">
+        <v>409</v>
+      </c>
+      <c r="I4">
+        <v>0.0106638418079096</v>
+      </c>
+      <c r="J4">
+        <v>0.01029707955689829</v>
+      </c>
+      <c r="M4">
+        <v>392</v>
+      </c>
+      <c r="N4">
+        <v>37</v>
+      </c>
+      <c r="O4">
+        <v>0.09438775510204081</v>
+      </c>
+      <c r="R4" t="b">
+        <v>1</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="s">
+        <v>102</v>
+      </c>
+      <c r="V4">
+        <v>2.265634804649193</v>
+      </c>
+      <c r="W4">
+        <v>2.156610516206523</v>
+      </c>
+      <c r="X4">
+        <v>2.327594084545863</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26">
+      <c r="A5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D5">
+        <v>0.2816848413979675</v>
+      </c>
+      <c r="E5">
+        <v>260822</v>
+      </c>
+      <c r="F5">
+        <v>74502</v>
+      </c>
+      <c r="G5">
+        <v>6006</v>
+      </c>
+      <c r="H5">
+        <v>832</v>
+      </c>
+      <c r="I5">
+        <v>0.02302719862588279</v>
+      </c>
+      <c r="J5">
+        <v>0.01116748543663257</v>
+      </c>
+      <c r="M5">
+        <v>806</v>
+      </c>
+      <c r="N5">
+        <v>41</v>
+      </c>
+      <c r="O5">
+        <v>0.05086848635235732</v>
+      </c>
+      <c r="R5" t="b">
+        <v>1</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="s">
+        <v>99</v>
+      </c>
+      <c r="V5">
+        <v>2.587380929596152</v>
+      </c>
+      <c r="W5">
+        <v>2.196021615422702</v>
+      </c>
+      <c r="X5">
+        <v>2.950863377432017</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26">
+      <c r="A6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D6">
+        <v>0.2816848413979675</v>
+      </c>
+      <c r="E6">
+        <v>18318</v>
+      </c>
+      <c r="F6">
+        <v>8460</v>
+      </c>
+      <c r="G6">
+        <v>1241</v>
+      </c>
+      <c r="H6">
+        <v>641</v>
+      </c>
+      <c r="I6">
+        <v>0.06774757069549077</v>
+      </c>
+      <c r="J6">
+        <v>0.07576832151300236</v>
+      </c>
+      <c r="M6">
+        <v>93</v>
+      </c>
+      <c r="N6">
+        <v>39</v>
+      </c>
+      <c r="O6">
+        <v>0.4193548387096774</v>
+      </c>
+      <c r="R6" t="b">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="s">
+        <v>100</v>
+      </c>
+      <c r="V6">
+        <v>2.741886352735525</v>
+      </c>
+      <c r="W6">
+        <v>2.69934632187279</v>
+      </c>
+      <c r="X6">
+        <v>2.78505939745596</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26">
+      <c r="A7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D7">
+        <v>0.2816848413979675</v>
+      </c>
+      <c r="E7">
+        <v>84960</v>
+      </c>
+      <c r="F7">
+        <v>23220</v>
+      </c>
+      <c r="G7">
+        <v>1091</v>
+      </c>
+      <c r="H7">
+        <v>193</v>
+      </c>
+      <c r="I7">
+        <v>0.01284133709981168</v>
+      </c>
+      <c r="J7">
+        <v>0.008311800172265288</v>
+      </c>
+      <c r="M7">
+        <v>256</v>
+      </c>
+      <c r="N7">
+        <v>26</v>
+      </c>
+      <c r="O7">
+        <v>0.1015625</v>
+      </c>
+      <c r="R7" t="b">
+        <v>1</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="s">
+        <v>102</v>
+      </c>
+      <c r="V7">
+        <v>2.919649833729247</v>
+      </c>
+      <c r="W7">
+        <v>2.779153781598118</v>
+      </c>
+      <c r="X7">
+        <v>2.999494741159642</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26">
+      <c r="A8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8">
+        <v>0.4913685210766353</v>
+      </c>
+      <c r="E8">
+        <v>260819</v>
+      </c>
+      <c r="F8">
+        <v>76853</v>
+      </c>
+      <c r="G8">
+        <v>331</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0.001269079323208815</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>889</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="R8" t="b">
+        <v>1</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="b">
+        <v>1</v>
+      </c>
+      <c r="U8" t="s">
+        <v>99</v>
+      </c>
+      <c r="V8">
+        <v>4.513404180814128</v>
+      </c>
+      <c r="W8">
+        <v>3.830720489137272</v>
+      </c>
+      <c r="X8">
+        <v>5.147459715872512</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26">
+      <c r="A9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D9">
+        <v>0.4913685210766353</v>
+      </c>
+      <c r="E9">
+        <v>18318</v>
+      </c>
+      <c r="F9">
+        <v>4080</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>49</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="R9" t="b">
+        <v>1</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="b">
+        <v>1</v>
+      </c>
+      <c r="U9" t="s">
+        <v>100</v>
+      </c>
+      <c r="V9">
+        <v>4.782922060759448</v>
+      </c>
+      <c r="W9">
+        <v>4.708715610927649</v>
+      </c>
+      <c r="X9">
+        <v>4.858232734309979</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26">
+      <c r="A10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D10">
+        <v>0.4913685210766353</v>
+      </c>
+      <c r="E10">
+        <v>84960</v>
+      </c>
+      <c r="F10">
+        <v>19380</v>
+      </c>
+      <c r="G10">
+        <v>12</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0.0001412429378531073</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>238</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="R10" t="b">
+        <v>1</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="b">
+        <v>1</v>
+      </c>
+      <c r="U10" t="s">
+        <v>101</v>
+      </c>
+      <c r="V10">
+        <v>5.093011089064362</v>
+      </c>
+      <c r="W10">
+        <v>4.84793103076174</v>
+      </c>
+      <c r="X10">
+        <v>5.232291832340656</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26">
+      <c r="A11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" t="s">
+        <v>96</v>
+      </c>
+      <c r="C11" t="s">
+        <v>116</v>
+      </c>
+      <c r="D11">
+        <v>0.218586137707535</v>
+      </c>
+      <c r="E11">
+        <v>260818</v>
+      </c>
+      <c r="F11">
+        <v>13079</v>
+      </c>
+      <c r="G11">
+        <v>14093</v>
+      </c>
+      <c r="H11">
+        <v>725</v>
+      </c>
+      <c r="I11">
+        <v>0.05403384735716093</v>
+      </c>
+      <c r="J11">
+        <v>0.05543237250554324</v>
+      </c>
+      <c r="M11">
+        <v>154</v>
+      </c>
+      <c r="N11">
+        <v>24</v>
+      </c>
+      <c r="O11">
+        <v>0.1558441558441558</v>
+      </c>
+      <c r="R11" t="b">
+        <v>0</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="b">
+        <v>0</v>
+      </c>
+      <c r="U11" t="s">
+        <v>99</v>
+      </c>
+      <c r="V11">
+        <v>2.007795667568483</v>
+      </c>
+      <c r="W11">
+        <v>1.704102644839638</v>
+      </c>
+      <c r="X11">
+        <v>2.289856370596061</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26">
+      <c r="A12" t="s">
+        <v>93</v>
+      </c>
+      <c r="B12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" t="s">
+        <v>116</v>
+      </c>
+      <c r="D12">
+        <v>0.218586137707535</v>
+      </c>
+      <c r="E12">
+        <v>18318</v>
+      </c>
+      <c r="F12">
+        <v>4440</v>
+      </c>
+      <c r="G12">
+        <v>1077</v>
+      </c>
+      <c r="H12">
+        <v>61</v>
+      </c>
+      <c r="I12">
+        <v>0.05879462823452342</v>
+      </c>
+      <c r="J12">
+        <v>0.01373873873873874</v>
+      </c>
+      <c r="M12">
+        <v>48</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>0.02083333333333333</v>
+      </c>
+      <c r="R12" t="b">
+        <v>1</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="b">
+        <v>0</v>
+      </c>
+      <c r="U12" t="s">
+        <v>100</v>
+      </c>
+      <c r="V12">
+        <v>2.127691163298016</v>
+      </c>
+      <c r="W12">
+        <v>2.094680295556264</v>
+      </c>
+      <c r="X12">
+        <v>2.161193246873688</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26">
+      <c r="A13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D13">
+        <v>0.218586137707535</v>
+      </c>
+      <c r="E13">
+        <v>84960</v>
+      </c>
+      <c r="F13">
+        <v>19020</v>
+      </c>
+      <c r="G13">
+        <v>707</v>
+      </c>
+      <c r="H13">
+        <v>89</v>
+      </c>
+      <c r="I13">
+        <v>0.008321563088512242</v>
+      </c>
+      <c r="J13">
+        <v>0.004679284963196635</v>
+      </c>
+      <c r="M13">
+        <v>230</v>
+      </c>
+      <c r="N13">
+        <v>10</v>
+      </c>
+      <c r="O13">
+        <v>0.04347826086956522</v>
+      </c>
+      <c r="R13" t="b">
+        <v>1</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="b">
+        <v>0</v>
+      </c>
+      <c r="U13" t="s">
+        <v>102</v>
+      </c>
+      <c r="V13">
+        <v>2.265634804649193</v>
+      </c>
+      <c r="W13">
+        <v>2.156610516206523</v>
+      </c>
+      <c r="X13">
+        <v>2.327594084545863</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26">
+      <c r="A14" t="s">
+        <v>94</v>
+      </c>
+      <c r="B14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" t="s">
+        <v>116</v>
+      </c>
+      <c r="D14">
+        <v>0.2816848413979675</v>
+      </c>
+      <c r="E14">
+        <v>260816</v>
+      </c>
+      <c r="F14">
+        <v>39360</v>
+      </c>
+      <c r="G14">
+        <v>8335</v>
+      </c>
+      <c r="H14">
+        <v>1217</v>
+      </c>
+      <c r="I14">
+        <v>0.03195739525182504</v>
+      </c>
+      <c r="J14">
+        <v>0.03091971544715447</v>
+      </c>
+      <c r="M14">
+        <v>479</v>
+      </c>
+      <c r="N14">
+        <v>35</v>
+      </c>
+      <c r="O14">
+        <v>0.07306889352818371</v>
+      </c>
+      <c r="R14" t="b">
+        <v>0</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="b">
+        <v>0</v>
+      </c>
+      <c r="U14" t="s">
+        <v>99</v>
+      </c>
+      <c r="V14">
+        <v>2.587380929596152</v>
+      </c>
+      <c r="W14">
+        <v>2.196021615422702</v>
+      </c>
+      <c r="X14">
+        <v>2.950863377432017</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26">
+      <c r="A15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D15">
+        <v>0.2816848413979675</v>
+      </c>
+      <c r="E15">
+        <v>18318</v>
+      </c>
+      <c r="F15">
+        <v>4200</v>
+      </c>
+      <c r="G15">
+        <v>32</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0.001746915602139972</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>53</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="R15" t="b">
+        <v>1</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="b">
+        <v>1</v>
+      </c>
+      <c r="U15" t="s">
+        <v>100</v>
+      </c>
+      <c r="V15">
+        <v>2.741886352735525</v>
+      </c>
+      <c r="W15">
+        <v>2.69934632187279</v>
+      </c>
+      <c r="X15">
+        <v>2.78505939745596</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26">
+      <c r="A16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" t="s">
+        <v>116</v>
+      </c>
+      <c r="D16">
+        <v>0.2816848413979675</v>
+      </c>
+      <c r="E16">
+        <v>84960</v>
+      </c>
+      <c r="F16">
+        <v>24420</v>
+      </c>
+      <c r="G16">
+        <v>121</v>
+      </c>
+      <c r="H16">
+        <v>36</v>
+      </c>
+      <c r="I16">
+        <v>0.001424199623352166</v>
+      </c>
+      <c r="J16">
+        <v>0.001474201474201474</v>
+      </c>
+      <c r="M16">
+        <v>272</v>
+      </c>
+      <c r="N16">
+        <v>4</v>
+      </c>
+      <c r="O16">
+        <v>0.01470588235294118</v>
+      </c>
+      <c r="R16" t="b">
+        <v>1</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="b">
+        <v>1</v>
+      </c>
+      <c r="U16" t="s">
+        <v>101</v>
+      </c>
+      <c r="V16">
+        <v>2.919649833729247</v>
+      </c>
+      <c r="W16">
+        <v>2.779153781598118</v>
+      </c>
+      <c r="X16">
+        <v>2.999494741159642</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26">
+      <c r="A17" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" t="s">
+        <v>96</v>
+      </c>
+      <c r="C17" t="s">
+        <v>116</v>
+      </c>
+      <c r="D17">
+        <v>0.4913685210766353</v>
+      </c>
+      <c r="E17">
+        <v>260828</v>
+      </c>
+      <c r="F17">
+        <v>43791</v>
+      </c>
+      <c r="G17">
+        <v>19357</v>
+      </c>
+      <c r="H17">
+        <v>1874</v>
+      </c>
+      <c r="I17">
+        <v>0.07421365804284816</v>
+      </c>
+      <c r="J17">
+        <v>0.04279418145280994</v>
+      </c>
+      <c r="M17">
+        <v>527</v>
+      </c>
+      <c r="N17">
+        <v>154</v>
+      </c>
+      <c r="O17">
+        <v>0.2922201138519924</v>
+      </c>
+      <c r="R17" t="b">
+        <v>0</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="b">
+        <v>0</v>
+      </c>
+      <c r="U17" t="s">
+        <v>99</v>
+      </c>
+      <c r="V17">
+        <v>4.513404180814128</v>
+      </c>
+      <c r="W17">
+        <v>3.830720489137272</v>
+      </c>
+      <c r="X17">
+        <v>5.147459715872512</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26">
+      <c r="A18" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" t="s">
+        <v>116</v>
+      </c>
+      <c r="D18">
+        <v>0.4913685210766353</v>
+      </c>
+      <c r="E18">
+        <v>18318</v>
+      </c>
+      <c r="F18">
+        <v>2880</v>
+      </c>
+      <c r="G18">
+        <v>2818</v>
+      </c>
+      <c r="H18">
+        <v>288</v>
+      </c>
+      <c r="I18">
+        <v>0.1538377552134512</v>
+      </c>
+      <c r="J18">
+        <v>0.1</v>
+      </c>
+      <c r="M18">
+        <v>41</v>
+      </c>
+      <c r="N18">
+        <v>29</v>
+      </c>
+      <c r="O18">
+        <v>0.7073170731707317</v>
+      </c>
+      <c r="R18" t="b">
+        <v>0</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="b">
+        <v>0</v>
+      </c>
+      <c r="U18" t="s">
+        <v>100</v>
+      </c>
+      <c r="V18">
+        <v>4.782922060759448</v>
+      </c>
+      <c r="W18">
+        <v>4.708715610927649</v>
+      </c>
+      <c r="X18">
+        <v>4.858232734309979</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26">
+      <c r="A19" t="s">
+        <v>95</v>
+      </c>
+      <c r="B19" t="s">
+        <v>98</v>
+      </c>
+      <c r="C19" t="s">
+        <v>116</v>
+      </c>
+      <c r="D19">
+        <v>0.4913685210766353</v>
+      </c>
+      <c r="E19">
+        <v>84960</v>
+      </c>
+      <c r="F19">
+        <v>9060</v>
+      </c>
+      <c r="G19">
+        <v>6852</v>
+      </c>
+      <c r="H19">
+        <v>1089</v>
+      </c>
+      <c r="I19">
+        <v>0.08064971751412429</v>
+      </c>
+      <c r="J19">
+        <v>0.1201986754966887</v>
+      </c>
+      <c r="M19">
+        <v>118</v>
+      </c>
+      <c r="N19">
+        <v>53</v>
+      </c>
+      <c r="O19">
+        <v>0.4491525423728814</v>
+      </c>
+      <c r="R19" t="b">
+        <v>0</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="b">
+        <v>0</v>
+      </c>
+      <c r="U19" t="s">
+        <v>102</v>
+      </c>
+      <c r="V19">
+        <v>5.093011089064362</v>
+      </c>
+      <c r="W19">
+        <v>4.84793103076174</v>
+      </c>
+      <c r="X19">
+        <v>5.232291832340656</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26">
+      <c r="A20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" t="s">
+        <v>96</v>
+      </c>
+      <c r="C20" t="s">
+        <v>117</v>
+      </c>
+      <c r="D20">
+        <v>0.2789373305</v>
+      </c>
+      <c r="E20">
+        <v>260820</v>
+      </c>
+      <c r="F20">
+        <v>49373</v>
+      </c>
+      <c r="G20">
+        <v>2955</v>
+      </c>
+      <c r="H20">
+        <v>390</v>
+      </c>
+      <c r="I20">
+        <v>0.01132965263400046</v>
+      </c>
+      <c r="J20">
+        <v>0.007899054138901828</v>
+      </c>
+      <c r="M20">
+        <v>532</v>
+      </c>
+      <c r="N20">
+        <v>10</v>
+      </c>
+      <c r="O20">
+        <v>0.01879699248120301</v>
+      </c>
+      <c r="R20" t="b">
+        <v>1</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="b">
+        <v>1</v>
+      </c>
+      <c r="U20" t="s">
+        <v>99</v>
+      </c>
+      <c r="V20">
+        <v>2.562144011393602</v>
+      </c>
+      <c r="W20">
+        <v>2.174601956165918</v>
+      </c>
+      <c r="X20">
+        <v>2.92208110697802</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26">
+      <c r="A21" t="s">
+        <v>90</v>
+      </c>
+      <c r="B21" t="s">
+        <v>97</v>
+      </c>
+      <c r="C21" t="s">
+        <v>117</v>
+      </c>
+      <c r="D21">
+        <v>0.2789373305</v>
+      </c>
+      <c r="E21">
+        <v>18318</v>
+      </c>
+      <c r="F21">
+        <v>6240</v>
+      </c>
+      <c r="G21">
+        <v>12</v>
+      </c>
+      <c r="H21">
+        <v>6</v>
+      </c>
+      <c r="I21">
+        <v>0.0006550933508024893</v>
+      </c>
+      <c r="J21">
+        <v>0.0009615384615384616</v>
+      </c>
+      <c r="M21">
+        <v>61</v>
+      </c>
+      <c r="N21">
+        <v>1</v>
+      </c>
+      <c r="O21">
+        <v>0.01639344262295082</v>
+      </c>
+      <c r="R21" t="b">
+        <v>1</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="b">
+        <v>1</v>
+      </c>
+      <c r="U21" t="s">
+        <v>100</v>
+      </c>
+      <c r="V21">
+        <v>2.715142412246069</v>
+      </c>
+      <c r="W21">
+        <v>2.673017310343711</v>
+      </c>
+      <c r="X21">
+        <v>2.757894353685692</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26">
+      <c r="A22" t="s">
+        <v>90</v>
+      </c>
+      <c r="B22" t="s">
+        <v>98</v>
+      </c>
+      <c r="C22" t="s">
+        <v>117</v>
+      </c>
+      <c r="D22">
+        <v>0.2789373305</v>
+      </c>
+      <c r="E22">
+        <v>84960</v>
+      </c>
+      <c r="F22">
+        <v>39720</v>
+      </c>
+      <c r="G22">
+        <v>84</v>
+      </c>
+      <c r="H22">
+        <v>38</v>
+      </c>
+      <c r="I22">
+        <v>0.0009887005649717514</v>
+      </c>
+      <c r="J22">
+        <v>0.0009566968781470292</v>
+      </c>
+      <c r="M22">
+        <v>392</v>
+      </c>
+      <c r="N22">
+        <v>4</v>
+      </c>
+      <c r="O22">
+        <v>0.01020408163265306</v>
+      </c>
+      <c r="R22" t="b">
+        <v>1</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="b">
+        <v>1</v>
+      </c>
+      <c r="U22" t="s">
+        <v>101</v>
+      </c>
+      <c r="V22">
+        <v>2.891172015410701</v>
+      </c>
+      <c r="W22">
+        <v>2.752046340302474</v>
+      </c>
+      <c r="X22">
+        <v>2.970238127815337</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26">
+      <c r="A23" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" t="s">
+        <v>117</v>
+      </c>
+      <c r="D23">
+        <v>0.3100300303</v>
+      </c>
+      <c r="E23">
+        <v>260822</v>
+      </c>
+      <c r="F23">
+        <v>74502</v>
+      </c>
+      <c r="G23">
+        <v>4163</v>
+      </c>
+      <c r="H23">
+        <v>458</v>
+      </c>
+      <c r="I23">
+        <v>0.01596107690302198</v>
+      </c>
+      <c r="J23">
+        <v>0.006147485973530912</v>
+      </c>
+      <c r="M23">
+        <v>806</v>
+      </c>
+      <c r="N23">
+        <v>21</v>
+      </c>
+      <c r="O23">
+        <v>0.0260545905707196</v>
+      </c>
+      <c r="R23" t="b">
+        <v>1</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="b">
+        <v>0</v>
+      </c>
+      <c r="U23" t="s">
+        <v>99</v>
+      </c>
+      <c r="V23">
+        <v>2.847742122079719</v>
+      </c>
+      <c r="W23">
+        <v>2.417001371426542</v>
+      </c>
+      <c r="X23">
+        <v>3.247800832221175</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26">
+      <c r="A24" t="s">
+        <v>91</v>
+      </c>
+      <c r="B24" t="s">
+        <v>97</v>
+      </c>
+      <c r="C24" t="s">
+        <v>117</v>
+      </c>
+      <c r="D24">
+        <v>0.3100300303</v>
+      </c>
+      <c r="E24">
+        <v>18318</v>
+      </c>
+      <c r="F24">
+        <v>8460</v>
+      </c>
+      <c r="G24">
+        <v>341</v>
+      </c>
+      <c r="H24">
+        <v>158</v>
+      </c>
+      <c r="I24">
+        <v>0.01861556938530407</v>
+      </c>
+      <c r="J24">
+        <v>0.01867612293144208</v>
+      </c>
+      <c r="M24">
+        <v>93</v>
+      </c>
+      <c r="N24">
+        <v>14</v>
+      </c>
+      <c r="O24">
+        <v>0.1505376344086022</v>
+      </c>
+      <c r="R24" t="b">
+        <v>1</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="b">
+        <v>0</v>
+      </c>
+      <c r="U24" t="s">
+        <v>100</v>
+      </c>
+      <c r="V24">
+        <v>3.017795010902866</v>
+      </c>
+      <c r="W24">
+        <v>2.970974291009375</v>
+      </c>
+      <c r="X24">
+        <v>3.065312443138097</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26">
+      <c r="A25" t="s">
+        <v>91</v>
+      </c>
+      <c r="B25" t="s">
+        <v>98</v>
+      </c>
+      <c r="C25" t="s">
+        <v>117</v>
+      </c>
+      <c r="D25">
+        <v>0.3100300303</v>
+      </c>
+      <c r="E25">
+        <v>84960</v>
+      </c>
+      <c r="F25">
+        <v>23220</v>
+      </c>
+      <c r="G25">
+        <v>223</v>
+      </c>
+      <c r="H25">
+        <v>21</v>
+      </c>
+      <c r="I25">
+        <v>0.002624764595103578</v>
+      </c>
+      <c r="J25">
+        <v>0.0009043927648578811</v>
+      </c>
+      <c r="M25">
+        <v>256</v>
+      </c>
+      <c r="N25">
+        <v>3</v>
+      </c>
+      <c r="O25">
+        <v>0.01171875</v>
+      </c>
+      <c r="R25" t="b">
+        <v>1</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="b">
+        <v>1</v>
+      </c>
+      <c r="U25" t="s">
+        <v>101</v>
+      </c>
+      <c r="V25">
+        <v>3.213446353464301</v>
+      </c>
+      <c r="W25">
+        <v>3.058812561020691</v>
+      </c>
+      <c r="X25">
+        <v>3.301325839442649</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26">
+      <c r="A26" t="s">
+        <v>92</v>
+      </c>
+      <c r="B26" t="s">
+        <v>96</v>
+      </c>
+      <c r="C26" t="s">
+        <v>117</v>
+      </c>
+      <c r="D26">
+        <v>0.5065765789</v>
+      </c>
+      <c r="E26">
+        <v>260819</v>
+      </c>
+      <c r="F26">
+        <v>76853</v>
+      </c>
+      <c r="G26">
+        <v>282</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0.001081209574455849</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>889</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="R26" t="b">
+        <v>1</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="b">
+        <v>1</v>
+      </c>
+      <c r="U26" t="s">
+        <v>99</v>
+      </c>
+      <c r="V26">
+        <v>4.653095896538285</v>
+      </c>
+      <c r="W26">
+        <v>3.94928286382155</v>
+      </c>
+      <c r="X26">
+        <v>5.306775711188826</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26">
+      <c r="A27" t="s">
+        <v>92</v>
+      </c>
+      <c r="B27" t="s">
+        <v>97</v>
+      </c>
+      <c r="C27" t="s">
+        <v>117</v>
+      </c>
+      <c r="D27">
+        <v>0.5065765789</v>
+      </c>
+      <c r="E27">
+        <v>18318</v>
+      </c>
+      <c r="F27">
+        <v>4080</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>49</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="R27" t="b">
+        <v>1</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="b">
+        <v>1</v>
+      </c>
+      <c r="U27" t="s">
+        <v>100</v>
+      </c>
+      <c r="V27">
+        <v>4.930955465718516</v>
+      </c>
+      <c r="W27">
+        <v>4.854452295743888</v>
+      </c>
+      <c r="X27">
+        <v>5.008597035590129</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26">
+      <c r="A28" t="s">
+        <v>92</v>
+      </c>
+      <c r="B28" t="s">
+        <v>98</v>
+      </c>
+      <c r="C28" t="s">
+        <v>117</v>
+      </c>
+      <c r="D28">
+        <v>0.5065765789</v>
+      </c>
+      <c r="E28">
+        <v>84960</v>
+      </c>
+      <c r="F28">
+        <v>19380</v>
+      </c>
+      <c r="G28">
+        <v>11</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0.0001294726930320151</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>238</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="R28" t="b">
+        <v>1</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="b">
+        <v>1</v>
+      </c>
+      <c r="U28" t="s">
+        <v>101</v>
+      </c>
+      <c r="V28">
+        <v>5.250641876986668</v>
+      </c>
+      <c r="W28">
+        <v>4.997976490080061</v>
+      </c>
+      <c r="X28">
+        <v>5.394233416552447</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="29" spans="1:26">
+      <c r="A29" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" t="s">
+        <v>96</v>
+      </c>
+      <c r="C29" t="s">
+        <v>117</v>
+      </c>
+      <c r="D29">
+        <v>0.2789373305</v>
+      </c>
+      <c r="E29">
+        <v>260818</v>
+      </c>
+      <c r="F29">
+        <v>13079</v>
+      </c>
+      <c r="G29">
+        <v>7069</v>
+      </c>
+      <c r="H29">
+        <v>235</v>
+      </c>
+      <c r="I29">
+        <v>0.0271031907307011</v>
+      </c>
+      <c r="J29">
+        <v>0.01796773453627953</v>
+      </c>
+      <c r="M29">
+        <v>154</v>
+      </c>
+      <c r="N29">
+        <v>12</v>
+      </c>
+      <c r="O29">
+        <v>0.07792207792207792</v>
+      </c>
+      <c r="R29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="b">
+        <v>0</v>
+      </c>
+      <c r="U29" t="s">
+        <v>99</v>
+      </c>
+      <c r="V29">
+        <v>2.562144011393602</v>
+      </c>
+      <c r="W29">
+        <v>2.174601956165918</v>
+      </c>
+      <c r="X29">
+        <v>2.92208110697802</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="30" spans="1:26">
+      <c r="A30" t="s">
+        <v>93</v>
+      </c>
+      <c r="B30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30" t="s">
+        <v>117</v>
+      </c>
+      <c r="D30">
+        <v>0.2789373305</v>
+      </c>
+      <c r="E30">
+        <v>18318</v>
+      </c>
+      <c r="F30">
+        <v>4440</v>
+      </c>
+      <c r="G30">
+        <v>406</v>
+      </c>
+      <c r="H30">
+        <v>32</v>
+      </c>
+      <c r="I30">
+        <v>0.02216399170215089</v>
+      </c>
+      <c r="J30">
+        <v>0.007207207207207207</v>
+      </c>
+      <c r="M30">
+        <v>48</v>
+      </c>
+      <c r="N30">
+        <v>1</v>
+      </c>
+      <c r="O30">
+        <v>0.02083333333333333</v>
+      </c>
+      <c r="R30" t="b">
+        <v>1</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="b">
+        <v>0</v>
+      </c>
+      <c r="U30" t="s">
+        <v>100</v>
+      </c>
+      <c r="V30">
+        <v>2.715142412246069</v>
+      </c>
+      <c r="W30">
+        <v>2.673017310343711</v>
+      </c>
+      <c r="X30">
+        <v>2.757894353685692</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="31" spans="1:26">
+      <c r="A31" t="s">
+        <v>93</v>
+      </c>
+      <c r="B31" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31" t="s">
+        <v>117</v>
+      </c>
+      <c r="D31">
+        <v>0.2789373305</v>
+      </c>
+      <c r="E31">
+        <v>84960</v>
+      </c>
+      <c r="F31">
+        <v>19020</v>
+      </c>
+      <c r="G31">
+        <v>108</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31">
+        <v>0.001271186440677966</v>
+      </c>
+      <c r="J31">
+        <v>5.257623554153522E-05</v>
+      </c>
+      <c r="M31">
+        <v>230</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="R31" t="b">
+        <v>1</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="b">
+        <v>1</v>
+      </c>
+      <c r="U31" t="s">
+        <v>101</v>
+      </c>
+      <c r="V31">
+        <v>2.891172015410701</v>
+      </c>
+      <c r="W31">
+        <v>2.752046340302474</v>
+      </c>
+      <c r="X31">
+        <v>2.970238127815337</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="32" spans="1:26">
+      <c r="A32" t="s">
+        <v>94</v>
+      </c>
+      <c r="B32" t="s">
+        <v>96</v>
+      </c>
+      <c r="C32" t="s">
+        <v>117</v>
+      </c>
+      <c r="D32">
+        <v>0.3100300303</v>
+      </c>
+      <c r="E32">
+        <v>260816</v>
+      </c>
+      <c r="F32">
+        <v>39360</v>
+      </c>
+      <c r="G32">
+        <v>6214</v>
+      </c>
+      <c r="H32">
+        <v>681</v>
+      </c>
+      <c r="I32">
+        <v>0.02382522544629164</v>
+      </c>
+      <c r="J32">
+        <v>0.01730182926829268</v>
+      </c>
+      <c r="M32">
+        <v>479</v>
+      </c>
+      <c r="N32">
+        <v>18</v>
+      </c>
+      <c r="O32">
+        <v>0.03757828810020877</v>
+      </c>
+      <c r="R32" t="b">
+        <v>1</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="b">
+        <v>0</v>
+      </c>
+      <c r="U32" t="s">
+        <v>99</v>
+      </c>
+      <c r="V32">
+        <v>2.847742122079719</v>
+      </c>
+      <c r="W32">
+        <v>2.417001371426542</v>
+      </c>
+      <c r="X32">
+        <v>3.247800832221175</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="33" spans="1:26">
+      <c r="A33" t="s">
+        <v>94</v>
+      </c>
+      <c r="B33" t="s">
+        <v>97</v>
+      </c>
+      <c r="C33" t="s">
+        <v>117</v>
+      </c>
+      <c r="D33">
+        <v>0.3100300303</v>
+      </c>
+      <c r="E33">
+        <v>18318</v>
+      </c>
+      <c r="F33">
+        <v>4200</v>
+      </c>
+      <c r="G33">
+        <v>13</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0.0007096844633693634</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>53</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="R33" t="b">
+        <v>1</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="b">
+        <v>1</v>
+      </c>
+      <c r="U33" t="s">
+        <v>100</v>
+      </c>
+      <c r="V33">
+        <v>3.017795010902866</v>
+      </c>
+      <c r="W33">
+        <v>2.970974291009375</v>
+      </c>
+      <c r="X33">
+        <v>3.065312443138097</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="34" spans="1:26">
+      <c r="A34" t="s">
+        <v>94</v>
+      </c>
+      <c r="B34" t="s">
+        <v>98</v>
+      </c>
+      <c r="C34" t="s">
+        <v>117</v>
+      </c>
+      <c r="D34">
+        <v>0.3100300303</v>
+      </c>
+      <c r="E34">
+        <v>84960</v>
+      </c>
+      <c r="F34">
+        <v>24420</v>
+      </c>
+      <c r="G34">
+        <v>58</v>
+      </c>
+      <c r="H34">
+        <v>8</v>
+      </c>
+      <c r="I34">
+        <v>0.0006826741996233521</v>
+      </c>
+      <c r="J34">
+        <v>0.0003276003276003276</v>
+      </c>
+      <c r="M34">
+        <v>272</v>
+      </c>
+      <c r="N34">
+        <v>1</v>
+      </c>
+      <c r="O34">
+        <v>0.003676470588235294</v>
+      </c>
+      <c r="R34" t="b">
+        <v>1</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="b">
+        <v>1</v>
+      </c>
+      <c r="U34" t="s">
+        <v>101</v>
+      </c>
+      <c r="V34">
+        <v>3.213446353464301</v>
+      </c>
+      <c r="W34">
+        <v>3.058812561020691</v>
+      </c>
+      <c r="X34">
+        <v>3.301325839442649</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="35" spans="1:26">
+      <c r="A35" t="s">
+        <v>95</v>
+      </c>
+      <c r="B35" t="s">
+        <v>96</v>
+      </c>
+      <c r="C35" t="s">
+        <v>117</v>
+      </c>
+      <c r="D35">
+        <v>0.5065765789</v>
+      </c>
+      <c r="E35">
+        <v>260828</v>
+      </c>
+      <c r="F35">
+        <v>43791</v>
+      </c>
+      <c r="G35">
+        <v>13835</v>
+      </c>
+      <c r="H35">
+        <v>1207</v>
+      </c>
+      <c r="I35">
+        <v>0.05304261812382106</v>
+      </c>
+      <c r="J35">
+        <v>0.0275627412025302</v>
+      </c>
+      <c r="M35">
+        <v>527</v>
+      </c>
+      <c r="N35">
+        <v>126</v>
+      </c>
+      <c r="O35">
+        <v>0.239089184060721</v>
+      </c>
+      <c r="R35" t="b">
+        <v>0</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="b">
+        <v>0</v>
+      </c>
+      <c r="U35" t="s">
+        <v>99</v>
+      </c>
+      <c r="V35">
+        <v>4.653095896538285</v>
+      </c>
+      <c r="W35">
+        <v>3.94928286382155</v>
+      </c>
+      <c r="X35">
+        <v>5.306775711188826</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="36" spans="1:26">
+      <c r="A36" t="s">
+        <v>95</v>
+      </c>
+      <c r="B36" t="s">
+        <v>97</v>
+      </c>
+      <c r="C36" t="s">
+        <v>117</v>
+      </c>
+      <c r="D36">
+        <v>0.5065765789</v>
+      </c>
+      <c r="E36">
+        <v>18318</v>
+      </c>
+      <c r="F36">
+        <v>2880</v>
+      </c>
+      <c r="G36">
+        <v>1868</v>
+      </c>
+      <c r="H36">
+        <v>166</v>
+      </c>
+      <c r="I36">
+        <v>0.1019761982749208</v>
+      </c>
+      <c r="J36">
+        <v>0.05763888888888889</v>
+      </c>
+      <c r="M36">
+        <v>41</v>
+      </c>
+      <c r="N36">
+        <v>24</v>
+      </c>
+      <c r="O36">
+        <v>0.5853658536585366</v>
+      </c>
+      <c r="R36" t="b">
+        <v>0</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="b">
+        <v>0</v>
+      </c>
+      <c r="U36" t="s">
+        <v>100</v>
+      </c>
+      <c r="V36">
+        <v>4.930955465718516</v>
+      </c>
+      <c r="W36">
+        <v>4.854452295743888</v>
+      </c>
+      <c r="X36">
+        <v>5.008597035590129</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="37" spans="1:26">
+      <c r="A37" t="s">
+        <v>95</v>
+      </c>
+      <c r="B37" t="s">
+        <v>98</v>
+      </c>
+      <c r="C37" t="s">
+        <v>117</v>
+      </c>
+      <c r="D37">
+        <v>0.5065765789</v>
+      </c>
+      <c r="E37">
+        <v>84960</v>
+      </c>
+      <c r="F37">
+        <v>9060</v>
+      </c>
+      <c r="G37">
+        <v>4420</v>
+      </c>
+      <c r="H37">
+        <v>691</v>
+      </c>
+      <c r="I37">
+        <v>0.05202448210922787</v>
+      </c>
+      <c r="J37">
+        <v>0.07626931567328918</v>
+      </c>
+      <c r="M37">
+        <v>118</v>
+      </c>
+      <c r="N37">
+        <v>46</v>
+      </c>
+      <c r="O37">
+        <v>0.3898305084745763</v>
+      </c>
+      <c r="R37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U37" t="s">
+        <v>102</v>
+      </c>
+      <c r="V37">
+        <v>5.250641876986668</v>
+      </c>
+      <c r="W37">
+        <v>4.997976490080061</v>
+      </c>
+      <c r="X37">
+        <v>5.394233416552447</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="38" spans="1:26">
+      <c r="A38" t="s">
+        <v>90</v>
+      </c>
+      <c r="B38" t="s">
+        <v>96</v>
+      </c>
+      <c r="C38" t="s">
+        <v>118</v>
+      </c>
+      <c r="D38">
+        <v>0.3737518551453107</v>
+      </c>
+      <c r="E38">
+        <v>260820</v>
+      </c>
+      <c r="F38">
+        <v>49373</v>
+      </c>
+      <c r="G38">
+        <v>1168</v>
+      </c>
+      <c r="H38">
+        <v>189</v>
+      </c>
+      <c r="I38">
+        <v>0.004478184188329116</v>
+      </c>
+      <c r="J38">
+        <v>0.003828003159621656</v>
+      </c>
+      <c r="M38">
+        <v>532</v>
+      </c>
+      <c r="N38">
+        <v>3</v>
+      </c>
+      <c r="O38">
+        <v>0.005639097744360902</v>
+      </c>
+      <c r="R38" t="b">
+        <v>1</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="b">
+        <v>1</v>
+      </c>
+      <c r="U38" t="s">
+        <v>99</v>
+      </c>
+      <c r="V38">
+        <v>3.433050985650724</v>
+      </c>
+      <c r="W38">
+        <v>2.913778209115087</v>
+      </c>
+      <c r="X38">
+        <v>3.915335508016909</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="39" spans="1:26">
+      <c r="A39" t="s">
+        <v>90</v>
+      </c>
+      <c r="B39" t="s">
+        <v>97</v>
+      </c>
+      <c r="C39" t="s">
+        <v>118</v>
+      </c>
+      <c r="D39">
+        <v>0.3737518551453107</v>
+      </c>
+      <c r="E39">
+        <v>18318</v>
+      </c>
+      <c r="F39">
+        <v>6240</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>61</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="R39" t="b">
+        <v>1</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="b">
+        <v>1</v>
+      </c>
+      <c r="U39" t="s">
+        <v>100</v>
+      </c>
+      <c r="V39">
+        <v>3.638055586685563</v>
+      </c>
+      <c r="W39">
+        <v>3.581611599944994</v>
+      </c>
+      <c r="X39">
+        <v>3.695339484095352</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="40" spans="1:26">
+      <c r="A40" t="s">
+        <v>90</v>
+      </c>
+      <c r="B40" t="s">
+        <v>98</v>
+      </c>
+      <c r="C40" t="s">
+        <v>118</v>
+      </c>
+      <c r="D40">
+        <v>0.3737518551453107</v>
+      </c>
+      <c r="E40">
+        <v>84960</v>
+      </c>
+      <c r="F40">
+        <v>39720</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>392</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="R40" t="b">
+        <v>1</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="b">
+        <v>1</v>
+      </c>
+      <c r="U40" t="s">
+        <v>101</v>
+      </c>
+      <c r="V40">
+        <v>3.873920003346257</v>
+      </c>
+      <c r="W40">
+        <v>3.687503652846181</v>
+      </c>
+      <c r="X40">
+        <v>3.979861743512013</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="41" spans="1:26">
+      <c r="A41" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" t="s">
+        <v>96</v>
+      </c>
+      <c r="C41" t="s">
+        <v>118</v>
+      </c>
+      <c r="D41">
+        <v>0.3406445469608993</v>
+      </c>
+      <c r="E41">
+        <v>260822</v>
+      </c>
+      <c r="F41">
+        <v>74502</v>
+      </c>
+      <c r="G41">
+        <v>2660</v>
+      </c>
+      <c r="H41">
+        <v>202</v>
+      </c>
+      <c r="I41">
+        <v>0.01019852619794342</v>
+      </c>
+      <c r="J41">
+        <v>0.002711336608413197</v>
+      </c>
+      <c r="M41">
+        <v>806</v>
+      </c>
+      <c r="N41">
+        <v>11</v>
+      </c>
+      <c r="O41">
+        <v>0.01364764267990074</v>
+      </c>
+      <c r="R41" t="b">
+        <v>1</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="b">
+        <v>1</v>
+      </c>
+      <c r="U41" t="s">
+        <v>99</v>
+      </c>
+      <c r="V41">
+        <v>3.128947941264372</v>
+      </c>
+      <c r="W41">
+        <v>2.655672859744473</v>
+      </c>
+      <c r="X41">
+        <v>3.568511224672851</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="42" spans="1:26">
+      <c r="A42" t="s">
+        <v>91</v>
+      </c>
+      <c r="B42" t="s">
+        <v>97</v>
+      </c>
+      <c r="C42" t="s">
+        <v>118</v>
+      </c>
+      <c r="D42">
+        <v>0.3406445469608993</v>
+      </c>
+      <c r="E42">
+        <v>18318</v>
+      </c>
+      <c r="F42">
+        <v>8460</v>
+      </c>
+      <c r="G42">
+        <v>71</v>
+      </c>
+      <c r="H42">
+        <v>40</v>
+      </c>
+      <c r="I42">
+        <v>0.003875968992248062</v>
+      </c>
+      <c r="J42">
+        <v>0.004728132387706856</v>
+      </c>
+      <c r="M42">
+        <v>93</v>
+      </c>
+      <c r="N42">
+        <v>3</v>
+      </c>
+      <c r="O42">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="R42" t="b">
+        <v>1</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="b">
+        <v>0</v>
+      </c>
+      <c r="U42" t="s">
+        <v>100</v>
+      </c>
+      <c r="V42">
+        <v>3.315793032420541</v>
+      </c>
+      <c r="W42">
+        <v>3.264348909730012</v>
+      </c>
+      <c r="X42">
+        <v>3.368002665664303</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="43" spans="1:26">
+      <c r="A43" t="s">
+        <v>91</v>
+      </c>
+      <c r="B43" t="s">
+        <v>98</v>
+      </c>
+      <c r="C43" t="s">
+        <v>118</v>
+      </c>
+      <c r="D43">
+        <v>0.3406445469608993</v>
+      </c>
+      <c r="E43">
+        <v>84960</v>
+      </c>
+      <c r="F43">
+        <v>23220</v>
+      </c>
+      <c r="G43">
+        <v>46</v>
+      </c>
+      <c r="H43">
+        <v>5</v>
+      </c>
+      <c r="I43">
+        <v>0.0005414312617702448</v>
+      </c>
+      <c r="J43">
+        <v>0.0002153316106804479</v>
+      </c>
+      <c r="M43">
+        <v>256</v>
+      </c>
+      <c r="N43">
+        <v>1</v>
+      </c>
+      <c r="O43">
+        <v>0.00390625</v>
+      </c>
+      <c r="R43" t="b">
+        <v>1</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="b">
+        <v>1</v>
+      </c>
+      <c r="U43" t="s">
+        <v>101</v>
+      </c>
+      <c r="V43">
+        <v>3.530764346278879</v>
+      </c>
+      <c r="W43">
+        <v>3.360860940080363</v>
+      </c>
+      <c r="X43">
+        <v>3.627321662546868</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="44" spans="1:26">
+      <c r="A44" t="s">
+        <v>92</v>
+      </c>
+      <c r="B44" t="s">
+        <v>96</v>
+      </c>
+      <c r="C44" t="s">
+        <v>118</v>
+      </c>
+      <c r="D44">
+        <v>0.5377193454913586</v>
+      </c>
+      <c r="E44">
+        <v>260819</v>
+      </c>
+      <c r="F44">
+        <v>76853</v>
+      </c>
+      <c r="G44">
+        <v>214</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0.000820492372104793</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>889</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="R44" t="b">
+        <v>1</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="b">
+        <v>1</v>
+      </c>
+      <c r="U44" t="s">
+        <v>99</v>
+      </c>
+      <c r="V44">
+        <v>4.939153889483329</v>
+      </c>
+      <c r="W44">
+        <v>4.192072600959251</v>
+      </c>
+      <c r="X44">
+        <v>5.633019924225902</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="45" spans="1:26">
+      <c r="A45" t="s">
+        <v>92</v>
+      </c>
+      <c r="B45" t="s">
+        <v>97</v>
+      </c>
+      <c r="C45" t="s">
+        <v>118</v>
+      </c>
+      <c r="D45">
+        <v>0.5377193454913586</v>
+      </c>
+      <c r="E45">
+        <v>18318</v>
+      </c>
+      <c r="F45">
+        <v>4080</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>49</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="R45" t="b">
+        <v>1</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="b">
+        <v>1</v>
+      </c>
+      <c r="U45" t="s">
+        <v>100</v>
+      </c>
+      <c r="V45">
+        <v>5.234095408498164</v>
+      </c>
+      <c r="W45">
+        <v>5.15288905944804</v>
+      </c>
+      <c r="X45">
+        <v>5.316510142761919</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="46" spans="1:26">
+      <c r="A46" t="s">
+        <v>92</v>
+      </c>
+      <c r="B46" t="s">
+        <v>98</v>
+      </c>
+      <c r="C46" t="s">
+        <v>118</v>
+      </c>
+      <c r="D46">
+        <v>0.5377193454913586</v>
+      </c>
+      <c r="E46">
+        <v>84960</v>
+      </c>
+      <c r="F46">
+        <v>19380</v>
+      </c>
+      <c r="G46">
+        <v>7</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>8.239171374764595E-05</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>238</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="R46" t="b">
+        <v>1</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="b">
+        <v>1</v>
+      </c>
+      <c r="U46" t="s">
+        <v>101</v>
+      </c>
+      <c r="V46">
+        <v>5.573435154924787</v>
+      </c>
+      <c r="W46">
+        <v>5.305236678850824</v>
+      </c>
+      <c r="X46">
+        <v>5.725854259734307</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="47" spans="1:26">
+      <c r="A47" t="s">
+        <v>93</v>
+      </c>
+      <c r="B47" t="s">
+        <v>96</v>
+      </c>
+      <c r="C47" t="s">
+        <v>118</v>
+      </c>
+      <c r="D47">
+        <v>0.3737518551453107</v>
+      </c>
+      <c r="E47">
+        <v>260818</v>
+      </c>
+      <c r="F47">
+        <v>13079</v>
+      </c>
+      <c r="G47">
+        <v>2771</v>
+      </c>
+      <c r="H47">
+        <v>7</v>
+      </c>
+      <c r="I47">
+        <v>0.01062426673005698</v>
+      </c>
+      <c r="J47">
+        <v>0.0005352091138466243</v>
+      </c>
+      <c r="M47">
+        <v>154</v>
+      </c>
+      <c r="N47">
+        <v>1</v>
+      </c>
+      <c r="O47">
+        <v>0.006493506493506494</v>
+      </c>
+      <c r="R47" t="b">
+        <v>1</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="b">
+        <v>1</v>
+      </c>
+      <c r="U47" t="s">
+        <v>99</v>
+      </c>
+      <c r="V47">
+        <v>3.433050985650724</v>
+      </c>
+      <c r="W47">
+        <v>2.913778209115087</v>
+      </c>
+      <c r="X47">
+        <v>3.915335508016909</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="48" spans="1:26">
+      <c r="A48" t="s">
+        <v>93</v>
+      </c>
+      <c r="B48" t="s">
+        <v>97</v>
+      </c>
+      <c r="C48" t="s">
+        <v>118</v>
+      </c>
+      <c r="D48">
+        <v>0.3737518551453107</v>
+      </c>
+      <c r="E48">
+        <v>18318</v>
+      </c>
+      <c r="F48">
+        <v>4440</v>
+      </c>
+      <c r="G48">
+        <v>25</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0.001364777814171853</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>48</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="R48" t="b">
+        <v>1</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="b">
+        <v>1</v>
+      </c>
+      <c r="U48" t="s">
+        <v>100</v>
+      </c>
+      <c r="V48">
+        <v>3.638055586685563</v>
+      </c>
+      <c r="W48">
+        <v>3.581611599944994</v>
+      </c>
+      <c r="X48">
+        <v>3.695339484095352</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="49" spans="1:26">
+      <c r="A49" t="s">
+        <v>93</v>
+      </c>
+      <c r="B49" t="s">
+        <v>98</v>
+      </c>
+      <c r="C49" t="s">
+        <v>118</v>
+      </c>
+      <c r="D49">
+        <v>0.3737518551453107</v>
+      </c>
+      <c r="E49">
+        <v>84960</v>
+      </c>
+      <c r="F49">
+        <v>19020</v>
+      </c>
+      <c r="G49">
+        <v>48</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0.0005649717514124294</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>230</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="R49" t="b">
+        <v>1</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="b">
+        <v>1</v>
+      </c>
+      <c r="U49" t="s">
+        <v>101</v>
+      </c>
+      <c r="V49">
+        <v>3.873920003346257</v>
+      </c>
+      <c r="W49">
+        <v>3.687503652846181</v>
+      </c>
+      <c r="X49">
+        <v>3.979861743512013</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="50" spans="1:26">
+      <c r="A50" t="s">
+        <v>94</v>
+      </c>
+      <c r="B50" t="s">
+        <v>96</v>
+      </c>
+      <c r="C50" t="s">
+        <v>118</v>
+      </c>
+      <c r="D50">
+        <v>0.3406445469608993</v>
+      </c>
+      <c r="E50">
+        <v>260816</v>
+      </c>
+      <c r="F50">
+        <v>39360</v>
+      </c>
+      <c r="G50">
+        <v>4804</v>
+      </c>
+      <c r="H50">
+        <v>457</v>
+      </c>
+      <c r="I50">
+        <v>0.01841911539169376</v>
+      </c>
+      <c r="J50">
+        <v>0.01161077235772358</v>
+      </c>
+      <c r="M50">
+        <v>479</v>
+      </c>
+      <c r="N50">
+        <v>10</v>
+      </c>
+      <c r="O50">
+        <v>0.0208768267223382</v>
+      </c>
+      <c r="R50" t="b">
+        <v>1</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="b">
+        <v>0</v>
+      </c>
+      <c r="U50" t="s">
+        <v>99</v>
+      </c>
+      <c r="V50">
+        <v>3.128947941264372</v>
+      </c>
+      <c r="W50">
+        <v>2.655672859744473</v>
+      </c>
+      <c r="X50">
+        <v>3.568511224672851</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="51" spans="1:26">
+      <c r="A51" t="s">
+        <v>94</v>
+      </c>
+      <c r="B51" t="s">
+        <v>97</v>
+      </c>
+      <c r="C51" t="s">
+        <v>118</v>
+      </c>
+      <c r="D51">
+        <v>0.3406445469608993</v>
+      </c>
+      <c r="E51">
+        <v>18318</v>
+      </c>
+      <c r="F51">
+        <v>4200</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>53</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="R51" t="b">
+        <v>1</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="b">
+        <v>1</v>
+      </c>
+      <c r="U51" t="s">
+        <v>100</v>
+      </c>
+      <c r="V51">
+        <v>3.315793032420541</v>
+      </c>
+      <c r="W51">
+        <v>3.264348909730012</v>
+      </c>
+      <c r="X51">
+        <v>3.368002665664303</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="52" spans="1:26">
+      <c r="A52" t="s">
+        <v>94</v>
+      </c>
+      <c r="B52" t="s">
+        <v>98</v>
+      </c>
+      <c r="C52" t="s">
+        <v>118</v>
+      </c>
+      <c r="D52">
+        <v>0.3406445469608993</v>
+      </c>
+      <c r="E52">
+        <v>84960</v>
+      </c>
+      <c r="F52">
+        <v>24420</v>
+      </c>
+      <c r="G52">
+        <v>38</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>0.0004472693032015066</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>272</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="R52" t="b">
+        <v>1</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="b">
+        <v>1</v>
+      </c>
+      <c r="U52" t="s">
+        <v>101</v>
+      </c>
+      <c r="V52">
+        <v>3.530764346278879</v>
+      </c>
+      <c r="W52">
+        <v>3.360860940080363</v>
+      </c>
+      <c r="X52">
+        <v>3.627321662546868</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="53" spans="1:26">
+      <c r="A53" t="s">
+        <v>95</v>
+      </c>
+      <c r="B53" t="s">
+        <v>96</v>
+      </c>
+      <c r="C53" t="s">
+        <v>118</v>
+      </c>
+      <c r="D53">
+        <v>0.5377193454913586</v>
+      </c>
+      <c r="E53">
+        <v>260828</v>
+      </c>
+      <c r="F53">
+        <v>43791</v>
+      </c>
+      <c r="G53">
+        <v>6100</v>
+      </c>
+      <c r="H53">
+        <v>398</v>
+      </c>
+      <c r="I53">
+        <v>0.02338705967150766</v>
+      </c>
+      <c r="J53">
+        <v>0.009088625516658674</v>
+      </c>
+      <c r="M53">
+        <v>527</v>
+      </c>
+      <c r="N53">
+        <v>59</v>
+      </c>
+      <c r="O53">
+        <v>0.1119544592030361</v>
+      </c>
+      <c r="R53" t="b">
+        <v>1</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="b">
+        <v>0</v>
+      </c>
+      <c r="U53" t="s">
+        <v>99</v>
+      </c>
+      <c r="V53">
+        <v>4.939153889483329</v>
+      </c>
+      <c r="W53">
+        <v>4.192072600959251</v>
+      </c>
+      <c r="X53">
+        <v>5.633019924225902</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="54" spans="1:26">
+      <c r="A54" t="s">
+        <v>95</v>
+      </c>
+      <c r="B54" t="s">
+        <v>97</v>
+      </c>
+      <c r="C54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D54">
+        <v>0.5377193454913586</v>
+      </c>
+      <c r="E54">
+        <v>18318</v>
+      </c>
+      <c r="F54">
+        <v>2880</v>
+      </c>
+      <c r="G54">
+        <v>685</v>
+      </c>
+      <c r="H54">
+        <v>36</v>
+      </c>
+      <c r="I54">
+        <v>0.03739491210830877</v>
+      </c>
+      <c r="J54">
+        <v>0.0125</v>
+      </c>
+      <c r="M54">
+        <v>41</v>
+      </c>
+      <c r="N54">
+        <v>10</v>
+      </c>
+      <c r="O54">
+        <v>0.2439024390243902</v>
+      </c>
+      <c r="R54" t="b">
+        <v>1</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="b">
+        <v>0</v>
+      </c>
+      <c r="U54" t="s">
+        <v>100</v>
+      </c>
+      <c r="V54">
+        <v>5.234095408498164</v>
+      </c>
+      <c r="W54">
+        <v>5.15288905944804</v>
+      </c>
+      <c r="X54">
+        <v>5.316510142761919</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="55" spans="1:26">
+      <c r="A55" t="s">
+        <v>95</v>
+      </c>
+      <c r="B55" t="s">
+        <v>98</v>
+      </c>
+      <c r="C55" t="s">
+        <v>118</v>
+      </c>
+      <c r="D55">
+        <v>0.5377193454913586</v>
+      </c>
+      <c r="E55">
+        <v>84960</v>
+      </c>
+      <c r="F55">
+        <v>9060</v>
+      </c>
+      <c r="G55">
+        <v>1466</v>
+      </c>
+      <c r="H55">
+        <v>190</v>
+      </c>
+      <c r="I55">
+        <v>0.01725517890772128</v>
+      </c>
+      <c r="J55">
+        <v>0.02097130242825607</v>
+      </c>
+      <c r="M55">
+        <v>118</v>
+      </c>
+      <c r="N55">
+        <v>27</v>
+      </c>
+      <c r="O55">
+        <v>0.2288135593220339</v>
+      </c>
+      <c r="R55" t="b">
+        <v>0</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="b">
+        <v>0</v>
+      </c>
+      <c r="U55" t="s">
+        <v>102</v>
+      </c>
+      <c r="V55">
+        <v>5.573435154924787</v>
+      </c>
+      <c r="W55">
+        <v>5.305236678850824</v>
+      </c>
+      <c r="X55">
+        <v>5.725854259734307</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>119</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Y37"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:25">
+      <c r="A1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25">
+      <c r="A2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D2">
+        <v>260820</v>
+      </c>
+      <c r="E2">
+        <v>49373</v>
+      </c>
+      <c r="F2">
+        <v>2955</v>
+      </c>
+      <c r="G2">
+        <v>390</v>
+      </c>
+      <c r="H2">
+        <v>0.01132965263400046</v>
+      </c>
+      <c r="I2">
+        <v>0.007899054138901828</v>
+      </c>
+      <c r="L2">
+        <v>532</v>
+      </c>
+      <c r="M2">
+        <v>10</v>
+      </c>
+      <c r="N2">
+        <v>0.01879699248120301</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" t="b">
+        <v>1</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="s">
+        <v>99</v>
+      </c>
+      <c r="U2">
+        <v>2.562144011393602</v>
+      </c>
+      <c r="V2">
+        <v>2.174601956165918</v>
+      </c>
+      <c r="W2">
+        <v>2.92208110697802</v>
+      </c>
+      <c r="X2" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25">
+      <c r="A3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3">
+        <v>18318</v>
+      </c>
+      <c r="E3">
+        <v>6240</v>
+      </c>
+      <c r="F3">
+        <v>12</v>
+      </c>
+      <c r="G3">
+        <v>6</v>
+      </c>
+      <c r="H3">
+        <v>0.0006550933508024893</v>
+      </c>
+      <c r="I3">
+        <v>0.0009615384615384616</v>
+      </c>
+      <c r="L3">
+        <v>61</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>0.01639344262295082</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" t="b">
+        <v>1</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="s">
+        <v>100</v>
+      </c>
+      <c r="U3">
+        <v>2.715142412246069</v>
+      </c>
+      <c r="V3">
+        <v>2.673017310343711</v>
+      </c>
+      <c r="W3">
+        <v>2.757894353685692</v>
+      </c>
+      <c r="X3" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
+      <c r="A4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D4">
+        <v>84960</v>
+      </c>
+      <c r="E4">
+        <v>39720</v>
+      </c>
+      <c r="F4">
+        <v>84</v>
+      </c>
+      <c r="G4">
+        <v>38</v>
+      </c>
+      <c r="H4">
+        <v>0.0009887005649717514</v>
+      </c>
+      <c r="I4">
+        <v>0.0009566968781470292</v>
+      </c>
+      <c r="L4">
+        <v>392</v>
+      </c>
+      <c r="M4">
+        <v>4</v>
+      </c>
+      <c r="N4">
+        <v>0.01020408163265306</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" t="b">
+        <v>1</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U4">
+        <v>2.891172015410701</v>
+      </c>
+      <c r="V4">
+        <v>2.752046340302474</v>
+      </c>
+      <c r="W4">
+        <v>2.970238127815337</v>
+      </c>
+      <c r="X4" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
+      <c r="A5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D5">
+        <v>260822</v>
+      </c>
+      <c r="E5">
+        <v>74502</v>
+      </c>
+      <c r="F5">
+        <v>4163</v>
+      </c>
+      <c r="G5">
+        <v>458</v>
+      </c>
+      <c r="H5">
+        <v>0.01596107690302198</v>
+      </c>
+      <c r="I5">
+        <v>0.006147485973530912</v>
+      </c>
+      <c r="L5">
+        <v>806</v>
+      </c>
+      <c r="M5">
+        <v>21</v>
+      </c>
+      <c r="N5">
+        <v>0.0260545905707196</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" t="b">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="s">
+        <v>99</v>
+      </c>
+      <c r="U5">
+        <v>2.847742122079719</v>
+      </c>
+      <c r="V5">
+        <v>2.417001371426542</v>
+      </c>
+      <c r="W5">
+        <v>3.247800832221175</v>
+      </c>
+      <c r="X5" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25">
+      <c r="A6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6">
+        <v>18318</v>
+      </c>
+      <c r="E6">
+        <v>8460</v>
+      </c>
+      <c r="F6">
+        <v>341</v>
+      </c>
+      <c r="G6">
+        <v>158</v>
+      </c>
+      <c r="H6">
+        <v>0.01861556938530407</v>
+      </c>
+      <c r="I6">
+        <v>0.01867612293144208</v>
+      </c>
+      <c r="L6">
+        <v>93</v>
+      </c>
+      <c r="M6">
+        <v>14</v>
+      </c>
+      <c r="N6">
+        <v>0.1505376344086022</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" t="b">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="s">
+        <v>100</v>
+      </c>
+      <c r="U6">
+        <v>3.017795010902866</v>
+      </c>
+      <c r="V6">
+        <v>2.970974291009375</v>
+      </c>
+      <c r="W6">
+        <v>3.065312443138097</v>
+      </c>
+      <c r="X6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
+      <c r="A7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D7">
+        <v>84960</v>
+      </c>
+      <c r="E7">
+        <v>23220</v>
+      </c>
+      <c r="F7">
+        <v>223</v>
+      </c>
+      <c r="G7">
+        <v>21</v>
+      </c>
+      <c r="H7">
+        <v>0.002624764595103578</v>
+      </c>
+      <c r="I7">
+        <v>0.0009043927648578811</v>
+      </c>
+      <c r="L7">
+        <v>256</v>
+      </c>
+      <c r="M7">
+        <v>3</v>
+      </c>
+      <c r="N7">
+        <v>0.01171875</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" t="b">
+        <v>1</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="s">
+        <v>101</v>
+      </c>
+      <c r="U7">
+        <v>3.213446353464301</v>
+      </c>
+      <c r="V7">
+        <v>3.058812561020691</v>
+      </c>
+      <c r="W7">
+        <v>3.301325839442649</v>
+      </c>
+      <c r="X7" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
+      <c r="A8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D8">
+        <v>260819</v>
+      </c>
+      <c r="E8">
+        <v>76853</v>
+      </c>
+      <c r="F8">
+        <v>282</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0.001081209574455849</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>889</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" t="b">
+        <v>1</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="s">
+        <v>99</v>
+      </c>
+      <c r="U8">
+        <v>4.653095896538285</v>
+      </c>
+      <c r="V8">
+        <v>3.94928286382155</v>
+      </c>
+      <c r="W8">
+        <v>5.306775711188826</v>
+      </c>
+      <c r="X8" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
+      <c r="A9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C9" t="s">
+        <v>122</v>
+      </c>
+      <c r="D9">
+        <v>18318</v>
+      </c>
+      <c r="E9">
+        <v>4080</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>49</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="b">
+        <v>1</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="s">
+        <v>100</v>
+      </c>
+      <c r="U9">
+        <v>4.930955465718516</v>
+      </c>
+      <c r="V9">
+        <v>4.854452295743888</v>
+      </c>
+      <c r="W9">
+        <v>5.008597035590129</v>
+      </c>
+      <c r="X9" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
+      <c r="A10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" t="s">
+        <v>122</v>
+      </c>
+      <c r="D10">
+        <v>84960</v>
+      </c>
+      <c r="E10">
+        <v>19380</v>
+      </c>
+      <c r="F10">
+        <v>11</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0.0001294726930320151</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>238</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="b">
+        <v>1</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="s">
+        <v>101</v>
+      </c>
+      <c r="U10">
+        <v>5.250641876986668</v>
+      </c>
+      <c r="V10">
+        <v>4.997976490080061</v>
+      </c>
+      <c r="W10">
+        <v>5.394233416552447</v>
+      </c>
+      <c r="X10" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
+      <c r="A11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" t="s">
+        <v>96</v>
+      </c>
+      <c r="C11" t="s">
+        <v>122</v>
+      </c>
+      <c r="D11">
+        <v>260818</v>
+      </c>
+      <c r="E11">
+        <v>13079</v>
+      </c>
+      <c r="F11">
+        <v>7069</v>
+      </c>
+      <c r="G11">
+        <v>235</v>
+      </c>
+      <c r="H11">
+        <v>0.0271031907307011</v>
+      </c>
+      <c r="I11">
+        <v>0.01796773453627953</v>
+      </c>
+      <c r="L11">
+        <v>154</v>
+      </c>
+      <c r="M11">
+        <v>12</v>
+      </c>
+      <c r="N11">
+        <v>0.07792207792207792</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="b">
+        <v>0</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="s">
+        <v>99</v>
+      </c>
+      <c r="U11">
+        <v>2.562144011393602</v>
+      </c>
+      <c r="V11">
+        <v>2.174601956165918</v>
+      </c>
+      <c r="W11">
+        <v>2.92208110697802</v>
+      </c>
+      <c r="X11" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25">
+      <c r="A12" t="s">
+        <v>93</v>
+      </c>
+      <c r="B12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D12">
+        <v>18318</v>
+      </c>
+      <c r="E12">
+        <v>4440</v>
+      </c>
+      <c r="F12">
+        <v>406</v>
+      </c>
+      <c r="G12">
+        <v>32</v>
+      </c>
+      <c r="H12">
+        <v>0.02216399170215089</v>
+      </c>
+      <c r="I12">
+        <v>0.007207207207207207</v>
+      </c>
+      <c r="L12">
+        <v>48</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>0.02083333333333333</v>
+      </c>
+      <c r="Q12" t="b">
+        <v>1</v>
+      </c>
+      <c r="R12" t="b">
+        <v>0</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="s">
+        <v>100</v>
+      </c>
+      <c r="U12">
+        <v>2.715142412246069</v>
+      </c>
+      <c r="V12">
+        <v>2.673017310343711</v>
+      </c>
+      <c r="W12">
+        <v>2.757894353685692</v>
+      </c>
+      <c r="X12" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
+      <c r="A13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C13" t="s">
+        <v>122</v>
+      </c>
+      <c r="D13">
+        <v>84960</v>
+      </c>
+      <c r="E13">
+        <v>19020</v>
+      </c>
+      <c r="F13">
+        <v>108</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>0.001271186440677966</v>
+      </c>
+      <c r="I13">
+        <v>5.257623554153522E-05</v>
+      </c>
+      <c r="L13">
+        <v>230</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="b">
+        <v>1</v>
+      </c>
+      <c r="R13" t="b">
+        <v>1</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="s">
+        <v>101</v>
+      </c>
+      <c r="U13">
+        <v>2.891172015410701</v>
+      </c>
+      <c r="V13">
+        <v>2.752046340302474</v>
+      </c>
+      <c r="W13">
+        <v>2.970238127815337</v>
+      </c>
+      <c r="X13" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25">
+      <c r="A14" t="s">
+        <v>94</v>
+      </c>
+      <c r="B14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" t="s">
+        <v>122</v>
+      </c>
+      <c r="D14">
+        <v>260816</v>
+      </c>
+      <c r="E14">
+        <v>39360</v>
+      </c>
+      <c r="F14">
+        <v>6214</v>
+      </c>
+      <c r="G14">
+        <v>681</v>
+      </c>
+      <c r="H14">
+        <v>0.02382522544629164</v>
+      </c>
+      <c r="I14">
+        <v>0.01730182926829268</v>
+      </c>
+      <c r="L14">
+        <v>479</v>
+      </c>
+      <c r="M14">
+        <v>18</v>
+      </c>
+      <c r="N14">
+        <v>0.03757828810020877</v>
+      </c>
+      <c r="Q14" t="b">
+        <v>1</v>
+      </c>
+      <c r="R14" t="b">
+        <v>0</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="s">
+        <v>99</v>
+      </c>
+      <c r="U14">
+        <v>2.847742122079719</v>
+      </c>
+      <c r="V14">
+        <v>2.417001371426542</v>
+      </c>
+      <c r="W14">
+        <v>3.247800832221175</v>
+      </c>
+      <c r="X14" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25">
+      <c r="A15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15" t="s">
+        <v>122</v>
+      </c>
+      <c r="D15">
+        <v>18318</v>
+      </c>
+      <c r="E15">
+        <v>4200</v>
+      </c>
+      <c r="F15">
+        <v>13</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0.0007096844633693634</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>53</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="b">
+        <v>1</v>
+      </c>
+      <c r="R15" t="b">
+        <v>1</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="s">
+        <v>100</v>
+      </c>
+      <c r="U15">
+        <v>3.017795010902866</v>
+      </c>
+      <c r="V15">
+        <v>2.970974291009375</v>
+      </c>
+      <c r="W15">
+        <v>3.065312443138097</v>
+      </c>
+      <c r="X15" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25">
+      <c r="A16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" t="s">
+        <v>122</v>
+      </c>
+      <c r="D16">
+        <v>84960</v>
+      </c>
+      <c r="E16">
+        <v>24420</v>
+      </c>
+      <c r="F16">
+        <v>58</v>
+      </c>
+      <c r="G16">
+        <v>8</v>
+      </c>
+      <c r="H16">
+        <v>0.0006826741996233521</v>
+      </c>
+      <c r="I16">
+        <v>0.0003276003276003276</v>
+      </c>
+      <c r="L16">
+        <v>272</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>0.003676470588235294</v>
+      </c>
+      <c r="Q16" t="b">
+        <v>1</v>
+      </c>
+      <c r="R16" t="b">
+        <v>1</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="s">
+        <v>101</v>
+      </c>
+      <c r="U16">
+        <v>3.213446353464301</v>
+      </c>
+      <c r="V16">
+        <v>3.058812561020691</v>
+      </c>
+      <c r="W16">
+        <v>3.301325839442649</v>
+      </c>
+      <c r="X16" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25">
+      <c r="A17" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" t="s">
+        <v>96</v>
+      </c>
+      <c r="C17" t="s">
+        <v>122</v>
+      </c>
+      <c r="D17">
+        <v>260828</v>
+      </c>
+      <c r="E17">
+        <v>43791</v>
+      </c>
+      <c r="F17">
+        <v>13835</v>
+      </c>
+      <c r="G17">
+        <v>1207</v>
+      </c>
+      <c r="H17">
+        <v>0.05304261812382106</v>
+      </c>
+      <c r="I17">
+        <v>0.0275627412025302</v>
+      </c>
+      <c r="L17">
+        <v>527</v>
+      </c>
+      <c r="M17">
+        <v>126</v>
+      </c>
+      <c r="N17">
+        <v>0.239089184060721</v>
+      </c>
+      <c r="Q17" t="b">
+        <v>0</v>
+      </c>
+      <c r="R17" t="b">
+        <v>0</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="s">
+        <v>99</v>
+      </c>
+      <c r="U17">
+        <v>4.653095896538285</v>
+      </c>
+      <c r="V17">
+        <v>3.94928286382155</v>
+      </c>
+      <c r="W17">
+        <v>5.306775711188826</v>
+      </c>
+      <c r="X17" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25">
+      <c r="A18" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" t="s">
+        <v>122</v>
+      </c>
+      <c r="D18">
+        <v>18318</v>
+      </c>
+      <c r="E18">
+        <v>2880</v>
+      </c>
+      <c r="F18">
+        <v>1868</v>
+      </c>
+      <c r="G18">
+        <v>166</v>
+      </c>
+      <c r="H18">
+        <v>0.1019761982749208</v>
+      </c>
+      <c r="I18">
+        <v>0.05763888888888889</v>
+      </c>
+      <c r="L18">
+        <v>41</v>
+      </c>
+      <c r="M18">
+        <v>24</v>
+      </c>
+      <c r="N18">
+        <v>0.5853658536585366</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>0</v>
+      </c>
+      <c r="R18" t="b">
+        <v>0</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="s">
+        <v>100</v>
+      </c>
+      <c r="U18">
+        <v>4.930955465718516</v>
+      </c>
+      <c r="V18">
+        <v>4.854452295743888</v>
+      </c>
+      <c r="W18">
+        <v>5.008597035590129</v>
+      </c>
+      <c r="X18" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25">
+      <c r="A19" t="s">
+        <v>95</v>
+      </c>
+      <c r="B19" t="s">
+        <v>98</v>
+      </c>
+      <c r="C19" t="s">
+        <v>122</v>
+      </c>
+      <c r="D19">
+        <v>84960</v>
+      </c>
+      <c r="E19">
+        <v>9060</v>
+      </c>
+      <c r="F19">
+        <v>4420</v>
+      </c>
+      <c r="G19">
+        <v>691</v>
+      </c>
+      <c r="H19">
+        <v>0.05202448210922787</v>
+      </c>
+      <c r="I19">
+        <v>0.07626931567328918</v>
+      </c>
+      <c r="L19">
+        <v>118</v>
+      </c>
+      <c r="M19">
+        <v>46</v>
+      </c>
+      <c r="N19">
+        <v>0.3898305084745763</v>
+      </c>
+      <c r="Q19" t="b">
+        <v>0</v>
+      </c>
+      <c r="R19" t="b">
+        <v>0</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="s">
+        <v>102</v>
+      </c>
+      <c r="U19">
+        <v>5.250641876986668</v>
+      </c>
+      <c r="V19">
+        <v>4.997976490080061</v>
+      </c>
+      <c r="W19">
+        <v>5.394233416552447</v>
+      </c>
+      <c r="X19" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25">
+      <c r="A20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" t="s">
+        <v>96</v>
+      </c>
+      <c r="C20" t="s">
+        <v>123</v>
+      </c>
+      <c r="D20">
+        <v>260820</v>
+      </c>
+      <c r="E20">
+        <v>49373</v>
+      </c>
+      <c r="F20">
+        <v>93</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0.0003565677478720957</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>532</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="b">
+        <v>1</v>
+      </c>
+      <c r="R20" t="b">
+        <v>1</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="s">
+        <v>99</v>
+      </c>
+      <c r="U20">
+        <v>8</v>
+      </c>
+      <c r="V20">
+        <v>8</v>
+      </c>
+      <c r="W20">
+        <v>8</v>
+      </c>
+      <c r="X20" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25">
+      <c r="A21" t="s">
+        <v>90</v>
+      </c>
+      <c r="B21" t="s">
+        <v>97</v>
+      </c>
+      <c r="C21" t="s">
+        <v>123</v>
+      </c>
+      <c r="D21">
+        <v>18318</v>
+      </c>
+      <c r="E21">
+        <v>6240</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>61</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="b">
+        <v>1</v>
+      </c>
+      <c r="R21" t="b">
+        <v>1</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="s">
+        <v>100</v>
+      </c>
+      <c r="U21">
+        <v>8</v>
+      </c>
+      <c r="V21">
+        <v>8</v>
+      </c>
+      <c r="W21">
+        <v>8</v>
+      </c>
+      <c r="X21" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25">
+      <c r="A22" t="s">
+        <v>90</v>
+      </c>
+      <c r="B22" t="s">
+        <v>98</v>
+      </c>
+      <c r="C22" t="s">
+        <v>123</v>
+      </c>
+      <c r="D22">
+        <v>84960</v>
+      </c>
+      <c r="E22">
+        <v>39720</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>392</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="b">
+        <v>1</v>
+      </c>
+      <c r="R22" t="b">
+        <v>1</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="s">
+        <v>101</v>
+      </c>
+      <c r="U22">
+        <v>8</v>
+      </c>
+      <c r="V22">
+        <v>8</v>
+      </c>
+      <c r="W22">
+        <v>8</v>
+      </c>
+      <c r="X22" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25">
+      <c r="A23" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" t="s">
+        <v>123</v>
+      </c>
+      <c r="D23">
+        <v>260822</v>
+      </c>
+      <c r="E23">
+        <v>74502</v>
+      </c>
+      <c r="F23">
+        <v>86</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0.0003297267868508025</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>806</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="b">
+        <v>1</v>
+      </c>
+      <c r="R23" t="b">
+        <v>1</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="s">
+        <v>99</v>
+      </c>
+      <c r="U23">
+        <v>8</v>
+      </c>
+      <c r="V23">
+        <v>8</v>
+      </c>
+      <c r="W23">
+        <v>8</v>
+      </c>
+      <c r="X23" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25">
+      <c r="A24" t="s">
+        <v>91</v>
+      </c>
+      <c r="B24" t="s">
+        <v>97</v>
+      </c>
+      <c r="C24" t="s">
+        <v>123</v>
+      </c>
+      <c r="D24">
+        <v>18318</v>
+      </c>
+      <c r="E24">
+        <v>8460</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>93</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="b">
+        <v>1</v>
+      </c>
+      <c r="R24" t="b">
+        <v>1</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="s">
+        <v>100</v>
+      </c>
+      <c r="U24">
+        <v>8</v>
+      </c>
+      <c r="V24">
+        <v>8</v>
+      </c>
+      <c r="W24">
+        <v>8</v>
+      </c>
+      <c r="X24" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25">
+      <c r="A25" t="s">
+        <v>91</v>
+      </c>
+      <c r="B25" t="s">
+        <v>98</v>
+      </c>
+      <c r="C25" t="s">
+        <v>123</v>
+      </c>
+      <c r="D25">
+        <v>84960</v>
+      </c>
+      <c r="E25">
+        <v>23220</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>256</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="b">
+        <v>1</v>
+      </c>
+      <c r="R25" t="b">
+        <v>1</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="s">
+        <v>101</v>
+      </c>
+      <c r="U25">
+        <v>8</v>
+      </c>
+      <c r="V25">
+        <v>8</v>
+      </c>
+      <c r="W25">
+        <v>8</v>
+      </c>
+      <c r="X25" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25">
+      <c r="A26" t="s">
+        <v>92</v>
+      </c>
+      <c r="B26" t="s">
+        <v>96</v>
+      </c>
+      <c r="C26" t="s">
+        <v>123</v>
+      </c>
+      <c r="D26">
+        <v>260819</v>
+      </c>
+      <c r="E26">
+        <v>76853</v>
+      </c>
+      <c r="F26">
+        <v>3</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>1.150222951548775E-05</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>889</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="b">
+        <v>1</v>
+      </c>
+      <c r="R26" t="b">
+        <v>1</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="s">
+        <v>99</v>
+      </c>
+      <c r="U26">
+        <v>8</v>
+      </c>
+      <c r="V26">
+        <v>8</v>
+      </c>
+      <c r="W26">
+        <v>8</v>
+      </c>
+      <c r="X26" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25">
+      <c r="A27" t="s">
+        <v>92</v>
+      </c>
+      <c r="B27" t="s">
+        <v>97</v>
+      </c>
+      <c r="C27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27">
+        <v>18318</v>
+      </c>
+      <c r="E27">
+        <v>4080</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>49</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="b">
+        <v>1</v>
+      </c>
+      <c r="R27" t="b">
+        <v>1</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="s">
+        <v>100</v>
+      </c>
+      <c r="U27">
+        <v>8</v>
+      </c>
+      <c r="V27">
+        <v>8</v>
+      </c>
+      <c r="W27">
+        <v>8</v>
+      </c>
+      <c r="X27" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25">
+      <c r="A28" t="s">
+        <v>92</v>
+      </c>
+      <c r="B28" t="s">
+        <v>98</v>
+      </c>
+      <c r="C28" t="s">
+        <v>123</v>
+      </c>
+      <c r="D28">
+        <v>84960</v>
+      </c>
+      <c r="E28">
+        <v>19380</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>238</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="b">
+        <v>1</v>
+      </c>
+      <c r="R28" t="b">
+        <v>1</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="s">
+        <v>101</v>
+      </c>
+      <c r="U28">
+        <v>8</v>
+      </c>
+      <c r="V28">
+        <v>8</v>
+      </c>
+      <c r="W28">
+        <v>8</v>
+      </c>
+      <c r="X28" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25">
+      <c r="A29" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" t="s">
+        <v>96</v>
+      </c>
+      <c r="C29" t="s">
+        <v>123</v>
+      </c>
+      <c r="D29">
+        <v>260818</v>
+      </c>
+      <c r="E29">
+        <v>13079</v>
+      </c>
+      <c r="F29">
+        <v>62</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0.0002377136547324188</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>154</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>1</v>
+      </c>
+      <c r="R29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="s">
+        <v>99</v>
+      </c>
+      <c r="U29">
+        <v>8</v>
+      </c>
+      <c r="V29">
+        <v>8</v>
+      </c>
+      <c r="W29">
+        <v>8</v>
+      </c>
+      <c r="X29" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25">
+      <c r="A30" t="s">
+        <v>93</v>
+      </c>
+      <c r="B30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30" t="s">
+        <v>123</v>
+      </c>
+      <c r="D30">
+        <v>18318</v>
+      </c>
+      <c r="E30">
+        <v>4440</v>
+      </c>
+      <c r="F30">
+        <v>15</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0.0008188666885031117</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>48</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="b">
+        <v>1</v>
+      </c>
+      <c r="R30" t="b">
+        <v>1</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="s">
+        <v>100</v>
+      </c>
+      <c r="U30">
+        <v>8</v>
+      </c>
+      <c r="V30">
+        <v>8</v>
+      </c>
+      <c r="W30">
+        <v>8</v>
+      </c>
+      <c r="X30" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25">
+      <c r="A31" t="s">
+        <v>93</v>
+      </c>
+      <c r="B31" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31" t="s">
+        <v>123</v>
+      </c>
+      <c r="D31">
+        <v>84960</v>
+      </c>
+      <c r="E31">
+        <v>19020</v>
+      </c>
+      <c r="F31">
+        <v>19</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0.0002236346516007533</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>230</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="b">
+        <v>1</v>
+      </c>
+      <c r="R31" t="b">
+        <v>1</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="s">
+        <v>101</v>
+      </c>
+      <c r="U31">
+        <v>8</v>
+      </c>
+      <c r="V31">
+        <v>8</v>
+      </c>
+      <c r="W31">
+        <v>8</v>
+      </c>
+      <c r="X31" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25">
+      <c r="A32" t="s">
+        <v>94</v>
+      </c>
+      <c r="B32" t="s">
+        <v>96</v>
+      </c>
+      <c r="C32" t="s">
+        <v>123</v>
+      </c>
+      <c r="D32">
+        <v>260816</v>
+      </c>
+      <c r="E32">
+        <v>39360</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>479</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="b">
+        <v>1</v>
+      </c>
+      <c r="R32" t="b">
+        <v>1</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="s">
+        <v>99</v>
+      </c>
+      <c r="U32">
+        <v>8</v>
+      </c>
+      <c r="V32">
+        <v>8</v>
+      </c>
+      <c r="W32">
+        <v>8</v>
+      </c>
+      <c r="X32" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25">
+      <c r="A33" t="s">
+        <v>94</v>
+      </c>
+      <c r="B33" t="s">
+        <v>97</v>
+      </c>
+      <c r="C33" t="s">
+        <v>123</v>
+      </c>
+      <c r="D33">
+        <v>18318</v>
+      </c>
+      <c r="E33">
+        <v>4200</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>53</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="b">
+        <v>1</v>
+      </c>
+      <c r="R33" t="b">
+        <v>1</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="s">
+        <v>100</v>
+      </c>
+      <c r="U33">
+        <v>8</v>
+      </c>
+      <c r="V33">
+        <v>8</v>
+      </c>
+      <c r="W33">
+        <v>8</v>
+      </c>
+      <c r="X33" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25">
+      <c r="A34" t="s">
+        <v>94</v>
+      </c>
+      <c r="B34" t="s">
+        <v>98</v>
+      </c>
+      <c r="C34" t="s">
+        <v>123</v>
+      </c>
+      <c r="D34">
+        <v>84960</v>
+      </c>
+      <c r="E34">
+        <v>24420</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>272</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="b">
+        <v>1</v>
+      </c>
+      <c r="R34" t="b">
+        <v>1</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="s">
+        <v>101</v>
+      </c>
+      <c r="U34">
+        <v>8</v>
+      </c>
+      <c r="V34">
+        <v>8</v>
+      </c>
+      <c r="W34">
+        <v>8</v>
+      </c>
+      <c r="X34" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25">
+      <c r="A35" t="s">
+        <v>95</v>
+      </c>
+      <c r="B35" t="s">
+        <v>96</v>
+      </c>
+      <c r="C35" t="s">
+        <v>123</v>
+      </c>
+      <c r="D35">
+        <v>260828</v>
+      </c>
+      <c r="E35">
+        <v>43791</v>
+      </c>
+      <c r="F35">
+        <v>117</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0.0004485714723879338</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>527</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="b">
+        <v>1</v>
+      </c>
+      <c r="R35" t="b">
+        <v>1</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="s">
+        <v>99</v>
+      </c>
+      <c r="U35">
+        <v>8</v>
+      </c>
+      <c r="V35">
+        <v>8</v>
+      </c>
+      <c r="W35">
+        <v>8</v>
+      </c>
+      <c r="X35" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25">
+      <c r="A36" t="s">
+        <v>95</v>
+      </c>
+      <c r="B36" t="s">
+        <v>97</v>
+      </c>
+      <c r="C36" t="s">
+        <v>123</v>
+      </c>
+      <c r="D36">
+        <v>18318</v>
+      </c>
+      <c r="E36">
+        <v>2880</v>
+      </c>
+      <c r="F36">
+        <v>16</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0.0008734578010699859</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>41</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="b">
+        <v>1</v>
+      </c>
+      <c r="R36" t="b">
+        <v>1</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="s">
+        <v>100</v>
+      </c>
+      <c r="U36">
+        <v>8</v>
+      </c>
+      <c r="V36">
+        <v>8</v>
+      </c>
+      <c r="W36">
+        <v>8</v>
+      </c>
+      <c r="X36" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25">
+      <c r="A37" t="s">
+        <v>95</v>
+      </c>
+      <c r="B37" t="s">
+        <v>98</v>
+      </c>
+      <c r="C37" t="s">
+        <v>123</v>
+      </c>
+      <c r="D37">
+        <v>84960</v>
+      </c>
+      <c r="E37">
+        <v>9060</v>
+      </c>
+      <c r="F37">
+        <v>24</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0.0002824858757062147</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>118</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="b">
+        <v>1</v>
+      </c>
+      <c r="R37" t="b">
+        <v>1</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="s">
+        <v>101</v>
+      </c>
+      <c r="U37">
+        <v>8</v>
+      </c>
+      <c r="V37">
+        <v>8</v>
+      </c>
+      <c r="W37">
+        <v>8</v>
+      </c>
+      <c r="X37" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>124</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -8952,10 +15179,10 @@
         <v>67</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -8966,7 +15193,7 @@
         <v>90</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D2">
         <v>211447</v>
@@ -8980,7 +15207,7 @@
         <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="D3">
         <v>520</v>
@@ -8994,7 +15221,7 @@
         <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D4">
         <v>49373</v>
@@ -9008,7 +15235,7 @@
         <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="D5">
         <v>3620</v>
@@ -9022,7 +15249,7 @@
         <v>91</v>
       </c>
       <c r="C6" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D6">
         <v>186320</v>
@@ -9036,7 +15263,7 @@
         <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="D7">
         <v>518</v>
@@ -9050,7 +15277,7 @@
         <v>91</v>
       </c>
       <c r="C8" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D8">
         <v>74502</v>
@@ -9064,7 +15291,7 @@
         <v>91</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="D9">
         <v>3620</v>
@@ -9078,7 +15305,7 @@
         <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D10">
         <v>183966</v>
@@ -9092,7 +15319,7 @@
         <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="D11">
         <v>521</v>
@@ -9106,7 +15333,7 @@
         <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D12">
         <v>76853</v>
@@ -9120,7 +15347,7 @@
         <v>92</v>
       </c>
       <c r="C13" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="D13">
         <v>3620</v>
@@ -9134,7 +15361,7 @@
         <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D14">
         <v>247739</v>
@@ -9148,7 +15375,7 @@
         <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="D15">
         <v>522</v>
@@ -9162,7 +15389,7 @@
         <v>93</v>
       </c>
       <c r="C16" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D16">
         <v>13079</v>
@@ -9176,7 +15403,7 @@
         <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="D17">
         <v>3620</v>
@@ -9190,7 +15417,7 @@
         <v>94</v>
       </c>
       <c r="C18" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D18">
         <v>221456</v>
@@ -9204,7 +15431,7 @@
         <v>94</v>
       </c>
       <c r="C19" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="D19">
         <v>524</v>
@@ -9218,7 +15445,7 @@
         <v>94</v>
       </c>
       <c r="C20" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D20">
         <v>39360</v>
@@ -9232,7 +15459,7 @@
         <v>94</v>
       </c>
       <c r="C21" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="D21">
         <v>3620</v>
@@ -9246,7 +15473,7 @@
         <v>95</v>
       </c>
       <c r="C22" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D22">
         <v>217037</v>
@@ -9260,7 +15487,7 @@
         <v>95</v>
       </c>
       <c r="C23" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="D23">
         <v>512</v>
@@ -9274,7 +15501,7 @@
         <v>95</v>
       </c>
       <c r="C24" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D24">
         <v>43791</v>
@@ -9288,7 +15515,7 @@
         <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="D25">
         <v>3620</v>
@@ -9302,7 +15529,7 @@
         <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D26">
         <v>12078</v>
@@ -9316,7 +15543,7 @@
         <v>90</v>
       </c>
       <c r="C27" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="D27">
         <v>402</v>
@@ -9330,7 +15557,7 @@
         <v>90</v>
       </c>
       <c r="C28" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D28">
         <v>6240</v>
@@ -9344,7 +15571,7 @@
         <v>91</v>
       </c>
       <c r="C29" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D29">
         <v>9858</v>
@@ -9358,7 +15585,7 @@
         <v>91</v>
       </c>
       <c r="C30" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="D30">
         <v>402</v>
@@ -9372,7 +15599,7 @@
         <v>91</v>
       </c>
       <c r="C31" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D31">
         <v>8460</v>
@@ -9386,7 +15613,7 @@
         <v>92</v>
       </c>
       <c r="C32" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D32">
         <v>14238</v>
@@ -9400,7 +15627,7 @@
         <v>92</v>
       </c>
       <c r="C33" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="D33">
         <v>402</v>
@@ -9414,7 +15641,7 @@
         <v>92</v>
       </c>
       <c r="C34" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D34">
         <v>4080</v>
@@ -9428,7 +15655,7 @@
         <v>93</v>
       </c>
       <c r="C35" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D35">
         <v>13878</v>
@@ -9442,7 +15669,7 @@
         <v>93</v>
       </c>
       <c r="C36" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="D36">
         <v>402</v>
@@ -9456,7 +15683,7 @@
         <v>93</v>
       </c>
       <c r="C37" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D37">
         <v>4440</v>
@@ -9470,7 +15697,7 @@
         <v>94</v>
       </c>
       <c r="C38" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D38">
         <v>14118</v>
@@ -9484,7 +15711,7 @@
         <v>94</v>
       </c>
       <c r="C39" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="D39">
         <v>402</v>
@@ -9498,7 +15725,7 @@
         <v>94</v>
       </c>
       <c r="C40" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D40">
         <v>4200</v>
@@ -9512,7 +15739,7 @@
         <v>95</v>
       </c>
       <c r="C41" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D41">
         <v>15438</v>
@@ -9526,7 +15753,7 @@
         <v>95</v>
       </c>
       <c r="C42" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="D42">
         <v>402</v>
@@ -9540,7 +15767,7 @@
         <v>95</v>
       </c>
       <c r="C43" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D43">
         <v>2880</v>
@@ -9554,7 +15781,7 @@
         <v>90</v>
       </c>
       <c r="C44" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D44">
         <v>45240</v>
@@ -9568,7 +15795,7 @@
         <v>90</v>
       </c>
       <c r="C45" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D45">
         <v>39720</v>
@@ -9582,7 +15809,7 @@
         <v>91</v>
       </c>
       <c r="C46" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D46">
         <v>61740</v>
@@ -9596,7 +15823,7 @@
         <v>91</v>
       </c>
       <c r="C47" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D47">
         <v>23220</v>
@@ -9610,7 +15837,7 @@
         <v>92</v>
       </c>
       <c r="C48" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D48">
         <v>65580</v>
@@ -9624,7 +15851,7 @@
         <v>92</v>
       </c>
       <c r="C49" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D49">
         <v>19380</v>
@@ -9638,7 +15865,7 @@
         <v>93</v>
       </c>
       <c r="C50" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D50">
         <v>65940</v>
@@ -9652,7 +15879,7 @@
         <v>93</v>
       </c>
       <c r="C51" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D51">
         <v>19020</v>
@@ -9666,7 +15893,7 @@
         <v>94</v>
       </c>
       <c r="C52" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D52">
         <v>60540</v>
@@ -9680,7 +15907,7 @@
         <v>94</v>
       </c>
       <c r="C53" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D53">
         <v>24420</v>
@@ -9694,7 +15921,7 @@
         <v>95</v>
       </c>
       <c r="C54" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D54">
         <v>75900</v>
@@ -9708,7 +15935,7 @@
         <v>95</v>
       </c>
       <c r="C55" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D55">
         <v>9060</v>
